--- a/data/trans_bre/IMC_inf_MED_R3-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IMC_inf_MED_R3-Edad-trans_bre.xlsx
@@ -604,19 +604,19 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>0.5664897698665128</v>
+        <v>6.214708666365359</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>3.131282933007346</v>
+        <v>6.4050781204465</v>
       </c>
       <c r="E4" s="5" t="n">
         <v>-0.4176033680120372</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>0.01604331972262261</v>
+        <v>0.2313258971998183</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.1105571920493414</v>
+        <v>0.2490050842218053</v>
       </c>
       <c r="H4" s="6" t="n">
         <v>-0.03076995294898967</v>
@@ -630,19 +630,19 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>-22.4703822933372</v>
+        <v>-11.11259515821681</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>-16.07220836738739</v>
+        <v>-13.06871339040396</v>
       </c>
       <c r="E5" s="5" t="n">
         <v>-21.99210217633286</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>-0.4673846206171894</v>
+        <v>-0.3047697264656462</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>-0.4359008379354903</v>
+        <v>-0.3852741812270992</v>
       </c>
       <c r="H5" s="6" t="inlineStr"/>
     </row>
@@ -654,19 +654,19 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>19.21966990567216</v>
+        <v>21.40925737495129</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>24.75518435593827</v>
+        <v>24.01906796868454</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>19.31667937314362</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0.7828895047746351</v>
+        <v>1.283939354531516</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>1.471331156833833</v>
+        <v>1.54351013340313</v>
       </c>
       <c r="H6" s="6" t="inlineStr"/>
     </row>
@@ -682,22 +682,22 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>-11.80519036404324</v>
+        <v>-9.52701983858239</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>-6.659098373217429</v>
+        <v>-6.458341266029108</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>-7.023318840950066</v>
+        <v>-6.8110709149935</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>-0.2674878113581414</v>
+        <v>-0.2424853633390107</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>-0.2307802231081865</v>
+        <v>-0.2501524470959778</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>-0.2134190346426726</v>
+        <v>-0.2111683279553193</v>
       </c>
     </row>
     <row r="8">
@@ -708,22 +708,22 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>-19.37077762449683</v>
+        <v>-15.94042638034399</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>-13.67479850388068</v>
+        <v>-12.39142834840501</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>-19.84775745769753</v>
+        <v>-18.45822397124803</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>-0.4104992652273863</v>
+        <v>-0.3803407026713138</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>-0.4199749598258241</v>
+        <v>-0.429262304498785</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>-0.5157114034337196</v>
+        <v>-0.4828202034170171</v>
       </c>
     </row>
     <row r="9">
@@ -734,22 +734,22 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>-3.775321689668694</v>
+        <v>-2.778057218863769</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>0.3148197020228282</v>
+        <v>0.1566900876461845</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>4.697034841866626</v>
+        <v>5.204211630265529</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>-0.097767357773758</v>
+        <v>-0.07691669618066199</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.01329063575322034</v>
+        <v>0.0211827768546901</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0.1781721777602554</v>
+        <v>0.2022810847989818</v>
       </c>
     </row>
     <row r="10">
@@ -764,22 +764,22 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>-2.491382474215967</v>
+        <v>-2.91953727460669</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>-16.24454766679096</v>
+        <v>-14.83639937285185</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>-12.74361179216131</v>
+        <v>-10.49968387983848</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>-0.1010074283955778</v>
+        <v>-0.1199279086304074</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>-0.6332228174163818</v>
+        <v>-0.615633479960405</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>-0.5132890351985474</v>
+        <v>-0.4513349372083858</v>
       </c>
     </row>
     <row r="11">
@@ -790,22 +790,22 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>-10.5812047267095</v>
+        <v>-11.13684445749297</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>-23.17240139328849</v>
+        <v>-21.35154891336393</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>-23.72142892547895</v>
+        <v>-20.33000150328405</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>-0.3604152936612119</v>
+        <v>-0.3979959163730924</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>-0.7772270264113929</v>
+        <v>-0.76102165043144</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>-0.7444070769475318</v>
+        <v>-0.7077830195697532</v>
       </c>
     </row>
     <row r="12">
@@ -816,22 +816,22 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>5.977408528958999</v>
+        <v>4.849716285235637</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>-9.632131856496269</v>
+        <v>-8.828251245961916</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>-2.883129892631895</v>
+        <v>-0.4390594258411524</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0.3125380604223728</v>
+        <v>0.2328815583940169</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>-0.4284660738334337</v>
+        <v>-0.4216783054849329</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>-0.08055084552020711</v>
+        <v>0.02552021718816182</v>
       </c>
     </row>
     <row r="13">
@@ -846,22 +846,22 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>-2.763092502044507</v>
+        <v>-1.241872861536875</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>-0.1335746506016658</v>
+        <v>-1.990727887572929</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>-5.191348324476219</v>
+        <v>-4.893085080403979</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>-0.3418516067884203</v>
+        <v>-0.1678396309644817</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>-0.02293875820145131</v>
+        <v>-0.2866357249386685</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>-0.5498530541469623</v>
+        <v>-0.5412635849940532</v>
       </c>
     </row>
     <row r="14">
@@ -872,22 +872,22 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>-7.48417145762715</v>
+        <v>-5.808898825829877</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>-4.739611318964782</v>
+        <v>-6.597839008164782</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>-12.28721076780367</v>
+        <v>-11.1443691785438</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>-0.7388373135696813</v>
+        <v>-0.5981215751269461</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>-0.5854156422165745</v>
+        <v>-0.691544927865074</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>-0.8451347888205567</v>
+        <v>-0.8517286336580282</v>
       </c>
     </row>
     <row r="15">
@@ -898,22 +898,22 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>1.986833701884626</v>
+        <v>2.740975918784898</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>4.168074776215725</v>
+        <v>2.344625167605724</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>0.8302304900306093</v>
+        <v>1.288427369206368</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>0.3965851996432518</v>
+        <v>0.6051496709929984</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>1.151083559606983</v>
+        <v>0.5771358023393385</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>0.4265373989621833</v>
+        <v>0.429927532593048</v>
       </c>
     </row>
     <row r="16">
@@ -928,22 +928,22 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>-6.259348845375815</v>
+        <v>-4.826569291150654</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>-7.554169948985562</v>
+        <v>-7.441287865984539</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>-8.257425787586413</v>
+        <v>-7.284750954182556</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>-0.2229787193260811</v>
+        <v>-0.1867183351947454</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>-0.3517942825767651</v>
+        <v>-0.3671751801100362</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>-0.4137454233637529</v>
+        <v>-0.3801287632498864</v>
       </c>
     </row>
     <row r="17">
@@ -954,22 +954,22 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>-10.8824037842611</v>
+        <v>-8.578672224337689</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>-11.27018647300211</v>
+        <v>-10.92596402798728</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>-13.45718379368242</v>
+        <v>-12.46873446246795</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>-0.3544774762113587</v>
+        <v>-0.3111706882688562</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>-0.4782752908541811</v>
+        <v>-0.4941096014565154</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>-0.5792645635859314</v>
+        <v>-0.5729224617793113</v>
       </c>
     </row>
     <row r="18">
@@ -980,22 +980,22 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>-1.641347644044664</v>
+        <v>-0.7260693950372041</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>-3.917953806249336</v>
+        <v>-3.97515238905609</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>-2.891569949231347</v>
+        <v>-2.422193359406978</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>-0.06625092445245986</v>
+        <v>-0.0301810895391834</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>-0.1927289360695908</v>
+        <v>-0.2161469352470453</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>-0.157786873515665</v>
+        <v>-0.1301259969326855</v>
       </c>
     </row>
     <row r="19">
